--- a/www/flightdata/xlsx/eoss-318.xlsx
+++ b/www/flightdata/xlsx/eoss-318.xlsx
@@ -3861,7 +3861,7 @@
         <v>32300.27</v>
       </c>
       <c r="I2">
-        <v>695</v>
+        <v>507</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
